--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/3218-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/3218-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{80CD34D2-E8CF-4122-8E31-3313719A0489}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{39F54C78-61F0-4AC1-89A9-6F67A0605399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{EB760759-B947-46D5-A608-0B75D084AAB4}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{84BCB720-6AEF-4E91-84F9-0F433C5B3F52}"/>
   </bookViews>
   <sheets>
     <sheet name="3218-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1400,18 +1400,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF0DAC69-9E50-473B-B7BF-13CED3194710}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C89C603-7160-4B38-AF08-A5F213031116}">
   <dimension ref="A1:R28"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="11.77734375" customWidth="1"/>
-    <col min="3" max="13" width="7.33203125" customWidth="1"/>
-    <col min="14" max="14" width="7.6640625" customWidth="1"/>
-    <col min="15" max="17" width="7.33203125" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="2" width="16.375" customWidth="1"/>
+    <col min="3" max="13" width="9" customWidth="1"/>
+    <col min="14" max="14" width="9.5" customWidth="1"/>
+    <col min="15" max="17" width="9" customWidth="1"/>
+    <col min="18" max="18" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
@@ -1439,7 +1439,7 @@
       <c r="Q1" s="27"/>
       <c r="R1" s="19"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="20" t="s">
         <v>1</v>
       </c>
@@ -1469,7 +1469,7 @@
       <c r="Q2" s="29"/>
       <c r="R2" s="30"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
         <v>2</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="22"/>
       <c r="B4" s="23"/>
       <c r="C4" s="7"/>
@@ -1565,7 +1565,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="34">
         <v>2025</v>
       </c>
@@ -1619,7 +1619,7 @@
         <v>3.29</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="36">
         <v>2024</v>
       </c>
@@ -1673,7 +1673,7 @@
         <v>2.69</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="34">
         <v>2023</v>
       </c>
@@ -1727,7 +1727,7 @@
         <v>1.84</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="36">
         <v>2022</v>
       </c>
@@ -1781,7 +1781,7 @@
         <v>2.0099999999999998</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="34">
         <v>2021</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v>1.42</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="36">
         <v>2020</v>
       </c>
@@ -1889,7 +1889,7 @@
         <v>2.62</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="34">
         <v>2019</v>
       </c>
@@ -1943,7 +1943,7 @@
         <v>3.58</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="36">
         <v>2018</v>
       </c>
@@ -1997,7 +1997,7 @@
         <v>4.13</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="34">
         <v>2017</v>
       </c>
@@ -2051,7 +2051,7 @@
         <v>4.45</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="36">
         <v>2016</v>
       </c>
@@ -2105,7 +2105,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="34">
         <v>2015</v>
       </c>
@@ -2159,7 +2159,7 @@
         <v>3.71</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="36">
         <v>2014</v>
       </c>
@@ -2213,7 +2213,7 @@
         <v>2.73</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="34">
         <v>2013</v>
       </c>
@@ -2267,7 +2267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="36">
         <v>2012</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>1.46</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="34">
         <v>2011</v>
       </c>
@@ -2375,7 +2375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="36">
         <v>2010</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="34">
         <v>2009</v>
       </c>
@@ -2483,7 +2483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="36">
         <v>2008</v>
       </c>
@@ -2537,7 +2537,7 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="34">
         <v>2007</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>2.35</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="36">
         <v>2006</v>
       </c>
@@ -2645,7 +2645,7 @@
         <v>5.09</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="34">
         <v>2005</v>
       </c>
@@ -2699,7 +2699,7 @@
         <v>3.22</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="36">
         <v>2004</v>
       </c>
@@ -2753,7 +2753,7 @@
         <v>2.97</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="34">
         <v>2003</v>
       </c>
@@ -2807,7 +2807,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="36" t="s">
         <v>25</v>
       </c>
